--- a/web/src/main/webapp/StorageYard/Other/UserDoc/Payroll/Staff Info for HRMS Demo1.xlsx
+++ b/web/src/main/webapp/StorageYard/Other/UserDoc/Payroll/Staff Info for HRMS Demo1.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="38" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Staff Info'!$A$2:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Staff Info'!$A$1:$H$4</definedName>
     <definedName name="EmpLevel" localSheetId="0">#REF!</definedName>
     <definedName name="EmpLevel">#REF!</definedName>
     <definedName name="ReasonforLeaving" localSheetId="0">#REF!</definedName>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Sr.No.</t>
   </si>
@@ -32,9 +32,6 @@
     <t>Mobile No</t>
   </si>
   <si>
-    <t>Staff Info 2018</t>
-  </si>
-  <si>
     <t>harshpatel3215@gmail.com</t>
   </si>
   <si>
@@ -96,13 +93,25 @@
   </si>
   <si>
     <t>11MNOPQ1234R2Z5</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>1,vadodara</t>
+  </si>
+  <si>
+    <t>2,vadodara</t>
+  </si>
+  <si>
+    <t>3,vadodara</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -148,15 +157,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,24 +167,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC61E"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF006B3F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -197,30 +187,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -264,28 +230,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -293,7 +247,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -605,147 +559,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="4" customWidth="1"/>
-    <col min="4" max="5" width="13.5703125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="37" style="4" customWidth="1"/>
-    <col min="7" max="7" width="25.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="60.140625" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="2" customWidth="1"/>
+    <col min="4" max="5" width="13.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37" style="2" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="60.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="25.140625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" ht="115.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="3"/>
+      <c r="G2" s="1">
+        <v>9979515243</v>
+      </c>
+      <c r="H2" s="1">
+        <v>9427240876</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" ht="115.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="1">
+        <v>9512287622</v>
+      </c>
+      <c r="H3" s="1">
+        <v>9712797929</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="G3" s="1">
-        <v>9979515243</v>
-      </c>
-      <c r="H3" s="1">
-        <v>9427240876</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>9512287622</v>
+        <v>9574119344</v>
       </c>
       <c r="H4" s="1">
-        <v>9712797929</v>
+        <v>9824669768</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="1">
-        <v>9574119344</v>
-      </c>
-      <c r="H5" s="1">
-        <v>9824669768</v>
-      </c>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H11" s="11"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F12" s="10"/>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F11" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H5"/>
+  <autoFilter ref="A1:H4"/>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" display="kevalbhatt29@gmail.com"/>
-    <hyperlink ref="F5" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F2" r:id="rId1" display="kevalbhatt29@gmail.com"/>
+    <hyperlink ref="F4" r:id="rId2"/>
+    <hyperlink ref="F3" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId4"/>
